--- a/2026/Security Analyst Job Research 2026.xlsx
+++ b/2026/Security Analyst Job Research 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/57509e41282bb22f/Desktop/Work/Role Research/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{8ACAD087-1016-413D-A608-45628FE2E67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4A824E7-EF3A-49E9-BCB9-43E70205ADEF}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="8_{8ACAD087-1016-413D-A608-45628FE2E67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF142143-0EB2-43E5-9006-FA58EE96049A}"/>
   <bookViews>
-    <workbookView xWindow="8260" yWindow="870" windowWidth="28800" windowHeight="17010" activeTab="2" xr2:uid="{8A2D5D1A-5EF9-48F7-BE7A-E9B82333B95F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{8A2D5D1A-5EF9-48F7-BE7A-E9B82333B95F}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="10" r:id="rId1"/>
@@ -27,15 +27,18 @@
     <definedName name="_xlchart.v1.0" hidden="1">Skills!$A$2:$A$47</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Skills!$C$1</definedName>
     <definedName name="_xlchart.v1.10" hidden="1">Certification!$E$1</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Certification!$E$2:$E$53</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Certification!$E$2:$E$55</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Skills!$A$2:$A$47</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Skills!$C$1</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">Skills!$C$2:$C$47</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">Skills!$C$2:$C$47</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Certification!$A$2:$A$53</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Certification!$A$2:$A$55</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">Certification!$E$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Certification!$E$2:$E$53</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Certification!$E$2:$E$55</definedName>
     <definedName name="_xlchart.v1.6" hidden="1">Skills!$A$2:$A$47</definedName>
     <definedName name="_xlchart.v1.7" hidden="1">Skills!$C$1</definedName>
     <definedName name="_xlchart.v1.8" hidden="1">Skills!$C$2:$C$47</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Certification!$A$2:$A$53</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Certification!$A$2:$A$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="399">
   <si>
     <t>Pay Range</t>
   </si>
@@ -217,9 +220,6 @@
     <t>Penetration Testing</t>
   </si>
   <si>
-    <t>Traver Requirement</t>
-  </si>
-  <si>
     <t>Clearance Requirement</t>
   </si>
   <si>
@@ -850,9 +850,6 @@
     <t>Weight</t>
   </si>
   <si>
-    <t>Security Analyst Research 2025</t>
-  </si>
-  <si>
     <t>Created By:</t>
   </si>
   <si>
@@ -955,12 +952,6 @@
     <t>https://www.cybermentordojo.com</t>
   </si>
   <si>
-    <t>4,5</t>
-  </si>
-  <si>
-    <t>1,4,5</t>
-  </si>
-  <si>
     <t>Currently In School</t>
   </si>
   <si>
@@ -1042,25 +1033,220 @@
     <t>2,3</t>
   </si>
   <si>
-    <t>1,5</t>
-  </si>
-  <si>
-    <t>1,3,5</t>
-  </si>
-  <si>
     <t>Soft Skills: Interpersonal Skills</t>
   </si>
   <si>
-    <t>1,2,3,4,5</t>
-  </si>
-  <si>
-    <t>1,3,4,5</t>
-  </si>
-  <si>
-    <t>1,2,4,5</t>
-  </si>
-  <si>
-    <t>3,5</t>
+    <t>Senior Security Analyst, Information Security</t>
+  </si>
+  <si>
+    <t>Norton Rose Fulbright</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4364012445</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>Security Analyst Research 2026</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4455956990/?eBP=NOT_ELIGIBLE_FOR_CHARGING&amp;trk=flagship3_search_srp_jobs&amp;refId=NGZmhv7z%2BaQyZ542F99Yqg%3D%3D&amp;trackingId=r1ZAlrRugZHWx%2FnmMGtERw%3D%3D</t>
+  </si>
+  <si>
+    <t>Optum / United Health Group</t>
+  </si>
+  <si>
+    <t>Associate Cyberecurity Analyst</t>
+  </si>
+  <si>
+    <t>5,9</t>
+  </si>
+  <si>
+    <t>Certified SOC Analyst</t>
+  </si>
+  <si>
+    <t>Travel Requirement</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4449952233/?alternateChannel=search&amp;eBP=CwEAAAGgHt7sFDg-LIfsSLboqiRwNERe0MQ4dowA5Nd30aM30ZSFcf3sCkJIcfnZmNlkL0ruQ5GKKcydAk-0-Lx9wnRAaunF9b3cmZzLYLw-wRlBK8n7DfBuWtPVx7txNI3VLA5JN7UaACik2P0VOkl_61NHSF5kzNIYc6Z5N_tPxYkCHb8MRraAfOrNuGhjGiGwuzF4PTvNxrebPtepaeTVmL-NCj5w21SCtguHtYc1SBInxLy17yZCUqijQwpNG8hbVPcqkRHuCqHtJvAsrTcXsa-SYmxz8_H5M5Vheep5wvxnDkKI78i-iImU_KIdfFTctvjnQIlc3ip2soDvA0IKho_ZTEK3Knlk3MdUcGZWRciPrWy4cuk87adXWoIlvfXwQfJDVTJG27dhzhkIbTYrNWGJAbgLaQ2K2pkIDJ3oG2ZBKp3ZlNo3hbqGHhNKBaHCksCOxunLAYba4XuxuQt-f2emD_eepk7EkQ0e56jfFgrZB9cy&amp;trk=d_flagship3_search_srp_jobs&amp;refId=NGZmhv7z%2BaQyZ542F99Yqg%3D%3D&amp;trackingId=%2BC67sS97wIbawPcMCWGy%2FA%3D%3D</t>
+  </si>
+  <si>
+    <t>Cyber Security Analyst I</t>
+  </si>
+  <si>
+    <t>Dallas College</t>
+  </si>
+  <si>
+    <t>Onsite</t>
+  </si>
+  <si>
+    <t>Mesquite, TX</t>
+  </si>
+  <si>
+    <t>9,10</t>
+  </si>
+  <si>
+    <t>5,10</t>
+  </si>
+  <si>
+    <t>1,10</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4429795044/?alternateChannel=search&amp;eBP=CwEAAAGgHt7sFKCIw7SrgZvMYrYpoXrm5OsU9IkMqw8lxvxO94uJD2ddE47CEkDnPRryU5eqf-SZpcru2Mka9q-EATkWjDDyEOn8rhmovZA7R29HPDVj5G2LZoJd8HdzPNNCsNv8WVHYN7vgElg6Ah674Mz9MZS2C9Zm7MKMwTa0C5u2NNTtVhKXEQyTBtOjhFdNE2ib5G7rXYUESqfjGaXQm_JUDIeJ5aPgVClJp8qvWJEowsZswzqk5x490EwdlheOzcDX0QDB2Rsw05d7-9a4_BOCmzCTLyjOhkgeBdXOMGME5uzHBzJBlSdq2SlNaLdacupcY0QsLfrQ24vXSK8yBZ96I0gyXl1EjUspaYk_JbAea_UqMFNAN_vwp2YJS5cmaY342T1WcyttcOhZYaK3zsFeMOYM0zyGrSYprkTATaEDx8iAjkJsvg8QFI2feY-lXxJEul5t4Gj7dmJZSiS6aCRKIlsOFft9zueP87kjwjOJL1T0&amp;trk=d_flagship3_search_srp_jobs&amp;refId=NGZmhv7z%2BaQyZ542F99Yqg%3D%3D&amp;trackingId=zeLNfyWljXAoVbWOsWLbKA%3D%3D</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Information Security Analyst</t>
+  </si>
+  <si>
+    <t>SpaceX</t>
+  </si>
+  <si>
+    <t>1,2,4,5,9,11</t>
+  </si>
+  <si>
+    <t>Yes 10%</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4453872945/?alternateChannel=search&amp;eBP=NOT_ELIGIBLE_FOR_CHARGING&amp;trk=d_flagship3_search_srp_jobs&amp;refId=NGZmhv7z%2BaQyZ542F99Yqg%3D%3D&amp;trackingId=rv5ZsqOlwrclSJESZ3BgfQ%3D%3D</t>
+  </si>
+  <si>
+    <t>Junior Cybersecurity Analyst</t>
+  </si>
+  <si>
+    <t>Stellar Gaming</t>
+  </si>
+  <si>
+    <t>New York City, New York</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4424181543/?alternateChannel=search&amp;eBP=CwEAAAGgHt7wNzyVPwrUdkIUWqg_FtgJYxuekxfv6QWXU5RyiIfl1-U4ySEIXThy6c20gdkuqDZULb_Cz7gtycckjeEisqRaXI76Gy7YhlD2d93O-rLQnLai6PmBhOh46m_vflyRPWVM2xRalGS2l1hFtPDI7IbIqQGocBJQSz5tkBFkoqd4Y_0C7tXu8cUT_R9eHYEnBDdjEjyuo1MZhrWJDYiwR9uqrzGJsSDVsP4DQkNrDFFaFdY-jBqJk9ez05rZeSKaefyCCxtgfSijnGIY-9z6yuw1VYx8XdLqZFfVIL8vexyhVGb5iHtLHxfQIbarblTY7P_euWzzkU0FjVbg_WsAtaygJV9-wuGtBG6ENHZl719ooGHAqtfD9KO063AVxIGqhVxC2BsoHF8d4EVuAWFBODowBAN2iftZ9uAd6HOnABqBSU2ptFKXgPx7-0u82andftvLEFVtPdsYfCcN6R_G4ZzlC3_w2zzY2_Ub2v5lkyluK2Q&amp;trk=d_flagship3_search_srp_jobs&amp;refId=Bh%2FQtIMAqLE0DqQY4LWuTQ%3D%3D&amp;trackingId=oRUhDphElSnmdNdFRGz6IA%3D%3D</t>
+  </si>
+  <si>
+    <t>Anaheim, CA</t>
+  </si>
+  <si>
+    <t>SAIC</t>
+  </si>
+  <si>
+    <t>80001-120000</t>
+  </si>
+  <si>
+    <t>11,13</t>
+  </si>
+  <si>
+    <t>9,10,12,13</t>
+  </si>
+  <si>
+    <t>4,11,13</t>
+  </si>
+  <si>
+    <t>1,5,11,13</t>
+  </si>
+  <si>
+    <t>9,12,13</t>
+  </si>
+  <si>
+    <t>1,4,5,9,10,11,12,13</t>
+  </si>
+  <si>
+    <t>4,5,10,11,13</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4448054923/?eBP=CwEAAAGgHt7wOMhSiaS-9S8JzXrhZykvML2Jx-L0-KZJ7wlYsmRj5TfmQF3wDe2TNM17kk4iMT0RLjvY92roITgiWE3Fj-kPhv1Q4gbS3qZZDEFfSaT8W2AjZLHwLSMZmu80wtDEu-53LX2L0-3U4ZThLiZEHteeTQqEWLG8pLUasJEZNQxw8CuiUFO7IoacpJeaB6seu14VZO8QJJxylNEAuXXr2WpdNFegxA32nHGvx_bw-2GknEs0Wq71J9H8an6wLVyZd81E8hkmTpEHxYychWGJnZ0c8FDTCGsj4KD3XyDXsQoWlNcPuXmWCe7J4kZw0hVfhiUFIBqB8QYezJKd40mv0l1O-lBP5xM7_LTkL1zEVRjruarmXg3-Cik364zEZECcP6EITCOo9IY1Tm5advLOyUS6zvRwBI5tD1EjQVvyaed4V8HB6RRd-SpKM6L0F3pHT-haoYKj3c__GQiF0brZNQUEyRy1e6Bf3f15e5KCTA&amp;trk=flagship3_search_srp_jobs&amp;refId=Bh%2FQtIMAqLE0DqQY4LWuTQ%3D%3D&amp;trackingId=71M0vL93x005hqHeazkUhA%3D%3D</t>
+  </si>
+  <si>
+    <t>SOC Analyst I</t>
+  </si>
+  <si>
+    <t>Heartland Business Systems</t>
+  </si>
+  <si>
+    <t>9,10,11,12,13,14</t>
+  </si>
+  <si>
+    <t>5,9,12,13,14</t>
+  </si>
+  <si>
+    <t>9,10,11,13,14</t>
+  </si>
+  <si>
+    <t>Microsoft Certified: Microsoft Identity and Access Administrator SC-300</t>
+  </si>
+  <si>
+    <t>2,9,14</t>
+  </si>
+  <si>
+    <t>Springfield, MO</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/jobs/view/4450631008/?alternateChannel=search&amp;eBP=CwEAAAGgHt7wOOE7v7q1RUgUsIXkZV2gNO6ad9CljdmP8-ofPFZnnT03Oq0-G7eYVAoQ0PtDq12jLsYIcbrRJ7NGcs8xQkBV9ML589HTsKZKURI6ZAWMgCdRtvXOZRez7I5NtFrnEG5vhvV62S4qm53RkhWk5Aq5VXB9iNBpmOV7_O_ygFw3DNKFsOteMys3fU-qc1cgtSI4hayzfSkcNZkwzJxljImCDskNvEtNe2b4VyxaXOXcb1914ZMAVOUVGHXjEmO4YUk46yLR1-f-8wE3WUYotSoMlOqOVqU1uRhGn3XSOWPI8VMf9NTB2f4vu2MBYcwYwujuAmDi3CV4DXr1hGkXuG1vd2TbXWhSjIPL8RuOjW-OlMeCCRHBIZ4n-akQnkBQGBBp_XIvG2Z-D91SYSlznwoASWBdndDNMycH0zG_i7P79cZwLw4Jp3Yakv1oRtmNNAvqDU302t0povvOANzuQyBcVa3JdzpphtBzMzptVIjrP0k&amp;trk=d_flagship3_search_srp_jobs&amp;refId=Bh%2FQtIMAqLE0DqQY4LWuTQ%3D%3D&amp;trackingId=SnymjP1g3yNUu9foKEn3AA%3D%3D</t>
+  </si>
+  <si>
+    <t>Moraine, OH</t>
+  </si>
+  <si>
+    <t>Cyber Security Analyst</t>
+  </si>
+  <si>
+    <t>Winsupply</t>
+  </si>
+  <si>
+    <t>1,5,10,11,12,14,15</t>
+  </si>
+  <si>
+    <t>1,3,5,9,10,11,12,13,14,15</t>
+  </si>
+  <si>
+    <t>8,9,10,12,13,14,15</t>
+  </si>
+  <si>
+    <t>10,12,13,14,15</t>
+  </si>
+  <si>
+    <t>9,10,14,15</t>
+  </si>
+  <si>
+    <t>11,13,15</t>
+  </si>
+  <si>
+    <t>9,11,12,13,14,15</t>
+  </si>
+  <si>
+    <t>5,9,10,11,14,15</t>
+  </si>
+  <si>
+    <t>9,14</t>
+  </si>
+  <si>
+    <t>1,9,12,15</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,9,10,11,12,13,14,15</t>
+  </si>
+  <si>
+    <t>1,3,4,5,9,10,11,12,13,14,15</t>
+  </si>
+  <si>
+    <t>3,5,9,10,11,12,14,15</t>
+  </si>
+  <si>
+    <t>3,10,12,13,15</t>
+  </si>
+  <si>
+    <t>10,11,12,13,14,15</t>
+  </si>
+  <si>
+    <t>5,10,14,15</t>
+  </si>
+  <si>
+    <t>9,13,15</t>
+  </si>
+  <si>
+    <t>3,12,15</t>
   </si>
 </sst>
 </file>
@@ -1435,59 +1621,122 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="47"/>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
                 <c:pt idx="8">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="32">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="29">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1</c:v>
-                </c:pt>
                 <c:pt idx="36">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="37">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1</c:v>
+                <c:pt idx="45">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1921,7 +2170,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Certification!$A$72:$A$74</c:f>
+              <c:f>Certification!$A$74:$A$76</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1938,15 +2187,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Certification!$B$72:$B$74</c:f>
+              <c:f>Certification!$B$74:$B$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>21</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>15</c:v>
@@ -2577,7 +2826,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Certification!$A$56:$A$69</c:f>
+              <c:f>Certification!$A$58:$A$71</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -2627,7 +2876,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Certification!$B$56:$B$69</c:f>
+              <c:f>Certification!$B$58:$B$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -2638,13 +2887,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -2653,13 +2902,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -2668,7 +2917,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -3363,23 +3612,35 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
+                <c:pt idx="9">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3885,23 +4146,35 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
+                <c:pt idx="9">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4214,6 +4487,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-B4F4-43E3-BB6F-A55724D340F0}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -4325,10 +4603,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
@@ -4938,7 +5219,7 @@
             <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
-            <c:showCatName val="0"/>
+            <c:showCatName val="1"/>
             <c:showSerName val="0"/>
             <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
@@ -4962,7 +5243,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Certification!$A$56:$A$69</c:f>
+              <c:f>Certification!$A$58:$A$71</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
@@ -5012,7 +5293,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Certification!$B$56:$B$69</c:f>
+              <c:f>Certification!$B$58:$B$71</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
@@ -5023,13 +5304,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5038,13 +5319,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -5053,7 +5334,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0</c:v>
@@ -5381,7 +5662,7 @@
             <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
-            <c:showCatName val="0"/>
+            <c:showCatName val="1"/>
             <c:showSerName val="0"/>
             <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
@@ -5405,7 +5686,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Certification!$A$72:$A$74</c:f>
+              <c:f>Certification!$A$74:$A$76</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -5422,15 +5703,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Certification!$B$72:$B$74</c:f>
+              <c:f>Certification!$B$74:$B$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>21</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>15</c:v>
@@ -5830,13 +6111,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1</c:v>
@@ -6265,59 +6549,122 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="47"/>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
                 <c:pt idx="5">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2</c:v>
                 </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
                 <c:pt idx="8">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="32">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="29">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1</c:v>
-                </c:pt>
                 <c:pt idx="36">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="37">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1</c:v>
+                <c:pt idx="45">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6939,13 +7286,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1</c:v>
@@ -7258,6 +7608,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-9C71-4708-BC49-26A12616E03D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
@@ -7343,6 +7698,9 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-9C71-4708-BC49-26A12616E03D}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:spPr>
@@ -7454,10 +7812,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
@@ -7676,7 +8037,7 @@
             <a:defRPr/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumMod val="65000"/>
@@ -7804,10 +8165,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.6</cx:f>
+        <cx:f>_xlchart.v1.12</cx:f>
       </cx:strDim>
       <cx:numDim type="size">
-        <cx:f>_xlchart.v1.8</cx:f>
+        <cx:f>_xlchart.v1.14</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -7842,7 +8203,7 @@
         <cx:series layoutId="treemap" uniqueId="{05B1019D-FB0E-4851-B74D-CE65FA35B4E8}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.7</cx:f>
+              <cx:f>_xlchart.v1.13</cx:f>
               <cx:v>Weight</cx:v>
             </cx:txData>
           </cx:tx>
@@ -17816,7 +18177,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="16533466" y="3323534"/>
-              <a:ext cx="10109753" cy="5331516"/>
+              <a:ext cx="10109753" cy="5515666"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -17932,13 +18293,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>158415</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>26738</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>1671</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>49797</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -17974,7 +18335,7 @@
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>16041</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>30079</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -18010,7 +18371,7 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -18817,42 +19178,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B1" t="s">
-        <v>267</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B3" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B4" s="13">
-        <v>45854</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -18867,7 +19228,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -18877,31 +19238,31 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
       <c r="B14" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" s="15" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B16" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
@@ -18953,7 +19314,7 @@
         <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -18983,16 +19344,16 @@
         <v>52</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>7</v>
@@ -19006,34 +19367,34 @@
         <v>28</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>53</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="M2" s="8">
         <v>100</v>
@@ -19045,7 +19406,7 @@
         <v>26</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8" t="s">
@@ -19060,34 +19421,34 @@
         <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="J3" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>53</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="M3" s="2">
         <v>100</v>
@@ -19099,7 +19460,7 @@
         <v>26</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="2" t="s">
@@ -19111,37 +19472,37 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="F4" s="8">
         <v>45</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>53</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M4" s="8">
         <v>100</v>
@@ -19153,7 +19514,7 @@
         <v>26</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q4" s="8"/>
       <c r="R4" s="8" t="s">
@@ -19165,19 +19526,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2">
         <v>55208.88</v>
@@ -19186,16 +19547,16 @@
         <v>88334.16</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>53</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="M5" s="2">
         <v>100</v>
@@ -19207,7 +19568,7 @@
         <v>26</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="2" t="s">
@@ -19219,37 +19580,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>53</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="M6" s="8">
         <v>100</v>
@@ -19261,7 +19622,7 @@
         <v>26</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8" t="s">
@@ -19273,19 +19634,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G7" s="2">
         <v>100000</v>
@@ -19294,16 +19655,16 @@
         <v>120000</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>53</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="M7" s="2">
         <v>100</v>
@@ -19315,7 +19676,7 @@
         <v>26</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2" t="s">
@@ -19327,19 +19688,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>318</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G8" s="8">
         <v>80000</v>
@@ -19348,16 +19709,16 @@
         <v>95000</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>53</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="M8" s="8">
         <v>100</v>
@@ -19369,7 +19730,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q8" s="8"/>
       <c r="R8" s="8" t="s">
@@ -19380,177 +19741,433 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="M9" s="2">
+        <v>30</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
+      <c r="R9" s="2" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>9</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
+      <c r="B10" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="M10" s="8">
+        <v>100</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>209</v>
+      </c>
       <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
+      <c r="R10" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="2">
+        <v>77200</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="M11" s="2">
+        <v>100</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
+      <c r="R11" s="2" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>11</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
+      <c r="B12" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="M12" s="8">
+        <v>100</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>209</v>
+      </c>
       <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
+      <c r="R12" s="8" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="M13" s="2">
+        <v>29</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
+      <c r="R13" s="8" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>13</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
+      <c r="B14" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="F14" s="8">
+        <v>80001</v>
+      </c>
+      <c r="G14" s="8">
+        <v>120000</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="M14" s="8">
+        <v>100</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>209</v>
+      </c>
       <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
+      <c r="R14" s="8" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="M15" s="2">
+        <v>100</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
+      <c r="R15" s="2" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>15</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
+      <c r="B16" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="M16" s="8">
+        <v>100</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>209</v>
+      </c>
       <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
+      <c r="R16" s="8" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
@@ -20327,6 +20944,9 @@
     <hyperlink ref="L6" r:id="rId1" xr:uid="{E874FF05-EE84-4AAC-888F-41325E5D1C8D}"/>
     <hyperlink ref="L7" r:id="rId2" xr:uid="{229BDEB1-1CDC-4095-8CAC-622EE1E22200}"/>
     <hyperlink ref="L8" r:id="rId3" xr:uid="{4E22A098-FDC4-4542-B648-7D0BF5EA5BC3}"/>
+    <hyperlink ref="L9" r:id="rId4" xr:uid="{1A4E08CB-D830-4206-9ACF-2C96D68E837B}"/>
+    <hyperlink ref="L10" r:id="rId5" xr:uid="{5A21EDF6-E0A5-4978-92F0-4C531C342A6F}"/>
+    <hyperlink ref="L13" r:id="rId6" xr:uid="{D0F4F6FA-C790-40C8-BBCC-308509F4CE05}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -20351,10 +20971,10 @@
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -20364,52 +20984,64 @@
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
       <c r="D3" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+        <v>142</v>
+      </c>
+      <c r="B4" s="8">
+        <v>9</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1</v>
+      </c>
       <c r="D4" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="B5" s="2">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
       <c r="D5" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B7" s="2">
         <v>5</v>
@@ -20418,88 +21050,96 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C8" s="8">
         <v>2</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
       <c r="D9" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>331</v>
+        <v>381</v>
       </c>
       <c r="C10" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C11" s="2">
+        <v>4</v>
+      </c>
       <c r="D11" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="8">
-        <v>5</v>
+        <v>66</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>345</v>
       </c>
       <c r="C12" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="2">
-        <v>4</v>
+        <v>102</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>363</v>
       </c>
       <c r="C13" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B14" s="8">
         <v>1</v>
@@ -20508,55 +21148,59 @@
         <v>1</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>331</v>
+        <v>364</v>
       </c>
       <c r="C15" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="2">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
       <c r="D17" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>332</v>
+        <v>382</v>
       </c>
       <c r="C18" s="8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -20566,179 +21210,231 @@
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="B20" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C20" s="8">
+        <v>7</v>
+      </c>
       <c r="D20" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C21" s="2">
+        <v>6</v>
+      </c>
       <c r="D21" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+        <v>67</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="C22" s="8">
+        <v>5</v>
+      </c>
       <c r="D22" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+      <c r="B23" s="2">
+        <v>10</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
       <c r="D23" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+        <v>127</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C24" s="8">
+        <v>4</v>
+      </c>
       <c r="D24" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="B25" s="2">
+        <v>13</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
       <c r="D25" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="B26" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C26" s="8">
+        <v>3</v>
+      </c>
       <c r="D26" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3</v>
+      </c>
       <c r="D27" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="B28" s="8">
+        <v>10</v>
+      </c>
+      <c r="C28" s="8">
+        <v>1</v>
+      </c>
       <c r="D28" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C29" s="2">
+        <v>6</v>
+      </c>
       <c r="D29" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="C30" s="8">
         <v>5</v>
       </c>
-      <c r="C30" s="8">
-        <v>1</v>
-      </c>
       <c r="D30" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B31" s="2">
-        <v>5</v>
+        <v>148</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>388</v>
       </c>
       <c r="C31" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
+      <c r="B32" s="8">
+        <v>14</v>
+      </c>
+      <c r="C32" s="8">
+        <v>1</v>
+      </c>
       <c r="D32" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C33" s="2">
+        <v>2</v>
+      </c>
       <c r="D33" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
+        <v>59</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="C34" s="8">
+        <v>5</v>
+      </c>
       <c r="D34" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="2">
-        <v>1</v>
+      <c r="B35" s="2" t="s">
+        <v>390</v>
       </c>
       <c r="C35" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -20748,101 +21444,105 @@
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
+      <c r="B37" s="2">
+        <v>10</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1</v>
+      </c>
       <c r="D37" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>334</v>
+        <v>391</v>
       </c>
       <c r="C38" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>334</v>
+      <c r="B39" s="2" t="s">
+        <v>391</v>
       </c>
       <c r="C39" s="8">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>334</v>
+      <c r="B40" s="2" t="s">
+        <v>391</v>
       </c>
       <c r="C40" s="10">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>335</v>
+        <v>392</v>
       </c>
       <c r="C41" s="8">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="C43" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
@@ -20852,41 +21552,45 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B45" s="8">
-        <v>3</v>
+      <c r="B45" s="8" t="s">
+        <v>394</v>
       </c>
       <c r="C45" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
+        <v>63</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="C47" s="8">
+        <v>6</v>
+      </c>
       <c r="D47" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -20927,7 +21631,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B2" s="2">
         <v>2</v>
@@ -20940,11 +21644,11 @@
       <c r="A3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="8">
-        <v>5</v>
+      <c r="B3" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="C3" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -20952,10 +21656,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>303</v>
+        <v>366</v>
       </c>
       <c r="C4" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -20969,8 +21673,12 @@
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="B6" s="2">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
@@ -20998,7 +21706,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD1CF6C-BB4A-403D-88AB-F5CBDE9621CB}">
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65" bestFit="1" customWidth="1"/>
@@ -21012,13 +21720,13 @@
         <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>29</v>
@@ -21026,1099 +21734,1139 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E2" s="8"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E6" s="8"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="8">
+        <v>9</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="8">
+        <v>9</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="8">
+        <v>9</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="8">
+        <v>15</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="2">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="8"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10" s="8"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="8" t="s">
+      <c r="C19" s="8"/>
+      <c r="D19" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" s="8"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14" s="8"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="E18" s="8"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="E20" s="8"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
+      <c r="C25" s="8"/>
+      <c r="D25" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="B22" s="8" t="s">
+      <c r="B27" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C27" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="8">
+        <v>15</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E29" s="8">
         <v>1</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" s="8">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="2">
+        <v>14</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E32" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C23" s="2">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="E24" s="8"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="8">
-        <v>1</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="E28" s="8"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="E30" s="8"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="E32" s="8"/>
-    </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E33" s="2"/>
+      <c r="A33" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E33" s="8"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>191</v>
+        <v>374</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C34" s="8"/>
+        <v>133</v>
+      </c>
+      <c r="C34" s="8">
+        <v>14</v>
+      </c>
       <c r="D34" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="E34" s="8"/>
+        <v>209</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E36" s="8"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
-        <v>129</v>
+        <v>207</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E38" s="8"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E40" s="8"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>125</v>
+        <v>209</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8" t="s">
-        <v>125</v>
+        <v>209</v>
       </c>
       <c r="E42" s="8"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>210</v>
+        <v>124</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>134</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8" t="s">
-        <v>210</v>
+        <v>124</v>
       </c>
       <c r="E44" s="8"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C45" s="2">
-        <v>5</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E45" s="2">
-        <v>1</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8" t="s">
-        <v>125</v>
+        <v>209</v>
       </c>
       <c r="E46" s="8"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="2"/>
+      <c r="C47" s="2" t="s">
+        <v>336</v>
+      </c>
       <c r="D47" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E47" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="E47" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8" t="s">
-        <v>210</v>
+        <v>124</v>
       </c>
       <c r="E48" s="8"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E50" s="8"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C51" s="2">
-        <v>5</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E51" s="2">
-        <v>1</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="E51" s="2"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E52" s="8"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E53" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B54" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E53" s="2"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E54" s="8"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B55" s="6"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56" s="8">
+      <c r="A55" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" s="6"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B58" s="8">
         <f>E2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B57" s="2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B59" s="2">
         <f>E3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B58" s="8">
-        <f>E4+E5+E7+E8+E6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B59" s="2">
-        <f>E10+E11+E12+E14+E15+E16+E13+E9</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="8" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B60" s="8">
-        <f>E17+E18</f>
-        <v>0</v>
+        <f>E4+E5+E7+E8+E6</f>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B61" s="2">
-        <f>E19</f>
-        <v>0</v>
+        <f>E11+E12+E13+E15+E16+E17+E14+E10</f>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B62" s="8">
+        <f>E18+E19</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B63" s="2">
         <f>E20</f>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B63" s="2">
-        <f>E22+E23+E24+E25+E21</f>
-        <v>2</v>
-      </c>
-    </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B64" s="8">
-        <f>E26+E28+E29+E27+E30</f>
-        <v>1</v>
+        <f>E21</f>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="B65" s="2">
-        <f>E35+E36+E37+E31+E33+E32+E34</f>
-        <v>0</v>
+        <f>E23+E24+E25+E26+E22</f>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B66" s="8">
-        <f>E39+E38</f>
-        <v>0</v>
+        <f>E27+E29+E30+E28+E31</f>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="B67" s="2">
-        <f>E40</f>
-        <v>0</v>
+        <f>E37+E38+E39+E32+E35+E33+E36</f>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B68" s="8">
-        <f>E40+E41+E43+E44+E45+E47+E48+E49+E50+E51+E52+E46</f>
-        <v>2</v>
+        <f>E41+E40</f>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B69" s="2">
-        <f>E53</f>
+        <f>E42</f>
         <v>0</v>
       </c>
     </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B70" s="8">
+        <f>E42+E43+E45+E46+E47+E49+E50+E51+E52+E53+E54+E48</f>
+        <v>4</v>
+      </c>
+    </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A71" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B71" s="6"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A72" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B72" s="8">
-        <f>COUNTIF(B2:B53,"Beginner")</f>
-        <v>21</v>
+      <c r="A71" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B71" s="2">
+        <f>E55</f>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A73" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B73" s="2">
-        <f>COUNTIF(B2:B53,"Intermediate")</f>
-        <v>16</v>
-      </c>
+      <c r="A73" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" s="6"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="8" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B74" s="8">
-        <f>COUNTIF(B2:B53,"Expert")</f>
+        <f>COUNTIF(B2:B55,"Beginner")</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B75" s="2">
+        <f>COUNTIF(B2:B55,"Intermediate")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B76" s="8">
+        <f>COUNTIF(B2:B55,"Expert")</f>
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A76" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A77" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E77" s="12"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="12"/>
-    </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A78" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>80</v>
+      <c r="A78" s="6" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B79" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="C79" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C79" s="8" t="s">
-        <v>154</v>
-      </c>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="C80" s="2" t="s">
-        <v>155</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B81" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B81" s="8" t="s">
-        <v>156</v>
-      </c>
       <c r="C81" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="C82" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B83" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C83" s="8" t="s">
         <v>156</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>222</v>
+        <v>157</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>161</v>
+        <v>221</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B89" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C89" s="8" t="s">
         <v>162</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="8" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C95" s="8" t="s">
         <v>169</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>170</v>
@@ -22126,76 +22874,76 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C99" s="8" t="s">
         <v>169</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>171</v>
@@ -22203,10 +22951,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>163</v>
@@ -22214,65 +22962,65 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C109" s="8" t="s">
         <v>173</v>
-      </c>
-      <c r="B109" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>175</v>
@@ -22280,142 +23028,142 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B117" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B117" s="8" t="s">
-        <v>178</v>
-      </c>
       <c r="C117" s="8" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="C118" s="2" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B119" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B119" s="8" t="s">
-        <v>178</v>
-      </c>
       <c r="C119" s="8" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="C120" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B121" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B121" s="8" t="s">
-        <v>183</v>
-      </c>
       <c r="C121" s="8" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>159</v>
@@ -22423,161 +23171,183 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B129" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C129" s="8" t="s">
         <v>185</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>223</v>
+        <v>180</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>224</v>
+        <v>156</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>171</v>
       </c>
     </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E53">
-    <sortCondition ref="A3:A53"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E55">
+    <sortCondition ref="A3:A55"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -22609,11 +23379,11 @@
       <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2" s="8">
         <v>3</v>
-      </c>
-      <c r="C2" s="8">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -22629,11 +23399,11 @@
       <c r="A4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="8">
-        <v>2</v>
+      <c r="B4" s="8" t="s">
+        <v>375</v>
       </c>
       <c r="C4" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -22641,9 +23411,11 @@
         <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
@@ -22681,7 +23453,7 @@
     </row>
     <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -22691,7 +23463,7 @@
       <c r="G2" s="17"/>
       <c r="H2" s="3"/>
       <c r="I2" s="17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J2" s="17"/>
       <c r="K2" s="17"/>
@@ -22701,7 +23473,7 @@
       <c r="O2" s="17"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R2" s="18"/>
       <c r="S2" s="18"/>
@@ -22733,7 +23505,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -22741,7 +23513,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -22749,7 +23521,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -22757,7 +23529,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -22765,7 +23537,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -22773,7 +23545,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -22781,7 +23553,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -22789,7 +23561,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -22797,7 +23569,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -22805,7 +23577,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -22813,7 +23585,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -22821,7 +23593,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -22829,7 +23601,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -22837,7 +23609,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -22845,7 +23617,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -22853,7 +23625,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -22868,47 +23640,47 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="15" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
@@ -22916,82 +23688,82 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="15" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="15" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="15" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="15" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
